--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B29537-9608-4A1D-BEEC-0768CB03C993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F2792B-3778-48B4-9CDB-ADA90E9DC89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -325,50 +325,50 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -661,12 +661,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="5.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.625" style="1" customWidth="1"/>
     <col min="4" max="5" width="5.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.375" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.125" style="1" customWidth="1"/>
     <col min="12" max="13" width="9" style="1" customWidth="1"/>
@@ -675,71 +675,71 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="22" t="s">
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="19"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="20" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
       <c r="K5" s="5" t="s">
         <v>8</v>
       </c>
@@ -769,10 +769,10 @@
       <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="14"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="4" t="s">
         <v>16</v>
       </c>
@@ -802,11 +802,11 @@
       <c r="H7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="25" t="s">
+      <c r="J7" s="15"/>
+      <c r="K7" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -819,9 +819,9 @@
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="25"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
@@ -832,9 +832,9 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="25"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
@@ -845,9 +845,9 @@
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="25"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
@@ -858,9 +858,9 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="25"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
@@ -871,9 +871,9 @@
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="25"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
@@ -884,22 +884,22 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="25"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="13" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="14"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="4" t="s">
         <v>28</v>
       </c>
@@ -914,15 +914,15 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="15" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="16"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="3" t="s">
         <v>33</v>
       </c>
@@ -937,15 +937,15 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="15" t="s">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="16"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="3" t="s">
         <v>38</v>
       </c>
@@ -960,61 +960,61 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="11" t="s">
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="17" t="s">
+      <c r="I17" s="15"/>
+      <c r="J17" s="21" t="s">
         <v>45</v>
       </c>
       <c r="K17" s="26"/>
     </row>
     <row r="18" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="11" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="11" t="s">
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="12"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="15"/>
     </row>
     <row r="19" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
       <c r="D19" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
       <c r="G19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="6" t="s">
         <v>52</v>
       </c>
@@ -1035,6 +1035,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="I12:J12"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="I8:J8"/>
@@ -1051,25 +1067,9 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I7:J7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/差旅报销单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F2792B-3778-48B4-9CDB-ADA90E9DC89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDD5226-44C3-4E95-A3B7-0CCE7E6F6CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,22 +328,40 @@
     <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -353,24 +371,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -668,43 +668,43 @@
     <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="5.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.25" style="1" customWidth="1"/>
     <col min="12" max="13" width="9" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24"/>
-      <c r="B3" s="13"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="18" t="s">
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="13"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
@@ -718,7 +718,7 @@
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="22" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="17"/>
@@ -726,20 +726,20 @@
       <c r="K4" s="17"/>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="5" t="s">
         <v>8</v>
       </c>
@@ -769,10 +769,10 @@
       <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="23"/>
+      <c r="J6" s="13"/>
       <c r="K6" s="4" t="s">
         <v>16</v>
       </c>
@@ -802,10 +802,10 @@
       <c r="H7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="11" t="s">
         <v>26</v>
       </c>
@@ -820,7 +820,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="14"/>
-      <c r="J8" s="15"/>
+      <c r="J8" s="12"/>
       <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -833,7 +833,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="15"/>
+      <c r="J9" s="12"/>
       <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -846,7 +846,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="14"/>
-      <c r="J10" s="15"/>
+      <c r="J10" s="12"/>
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -859,7 +859,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
+      <c r="J11" s="12"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -872,7 +872,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="15"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -885,21 +885,21 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
+      <c r="J13" s="12"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="22" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="23"/>
+      <c r="G14" s="13"/>
       <c r="H14" s="4" t="s">
         <v>28</v>
       </c>
@@ -914,11 +914,11 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="16" t="s">
         <v>32</v>
       </c>
@@ -937,11 +937,11 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="16" t="s">
         <v>37</v>
       </c>
@@ -960,61 +960,61 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
       <c r="H17" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="21" t="s">
+      <c r="I17" s="12"/>
+      <c r="J17" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K17" s="26"/>
+      <c r="K17" s="19"/>
     </row>
     <row r="18" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
       <c r="H18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="15"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
       <c r="D19" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
       <c r="G19" s="7" t="s">
         <v>51</v>
       </c>
       <c r="H19" s="14"/>
-      <c r="I19" s="15"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="6" t="s">
         <v>52</v>
       </c>
@@ -1035,22 +1035,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="I12:J12"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="I8:J8"/>
@@ -1067,6 +1051,22 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="E19:F19"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.51180555555555551" footer="0.51180555555555551"/>
